--- a/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
+++ b/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system.npz</t>
+          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system_nonlinear.npz</t>
         </is>
       </c>
     </row>

--- a/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
+++ b/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system_nonlinear.npz</t>
+          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/examples/sixdrive12resp/results/sdynpy_frame6x12_system_nonlinear_allmodes.npz</t>
         </is>
       </c>
     </row>

--- a/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
+++ b/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-67180" yWindow="1540" windowWidth="34560" windowHeight="21680" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Channel Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hardware" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Frame 6x12 Random" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Test Profile" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Channel Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hardware" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frame 6x12 Random" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Profile" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/control_laws/optimal_diagonal_control.py</t>
+          <t>/Users/nhunterjr/Documents/Code/python/rattlesnake-vibration-controller/control_laws/octave_band_switching_control.py</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>optimal_diagonal_control</t>
+          <t>octave_band_switching_control</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1e-6,0.05,20,1.0,0.95</t>
+          <t>1e-6,0.05,20,1.0,0.95,1.0,0.0,6</t>
         </is>
       </c>
     </row>

--- a/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
+++ b/examples/sixdrive12resp/results/sdynpy_frame6x12_profile.xlsx
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
